--- a/data/Original_data/2_raw data_unsigned_reference.xlsx
+++ b/data/Original_data/2_raw data_unsigned_reference.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/genhong_gao_ufl_edu/Documents/Documents/PhD/PhD Programs/SDG/2_cities SDGs 082024/Statistical Analysis/Final_Data_082025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="11_F25DC773A252ABDACC1048C371DE6ECC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91954EBB-8C41-4CED-B76C-334D247963CC}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="11_F25DC773A252ABDACC1048C371DE6ECC5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B401F9-D103-4693-9127-31CB45460B75}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1560" windowWidth="21012" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="204" yWindow="3072" windowWidth="24372" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -251,10 +251,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,10 +538,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>3.7</v>
+        <v>3.6500000953674299</v>
       </c>
       <c r="C2">
-        <v>21.1</v>
+        <v>21.100000381469702</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -556,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>14.3</v>
+        <v>14.300000190734863</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -600,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>17.8</v>
+        <v>17.847675323486328</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -611,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>34.700000000000003</v>
+        <v>34.681709289550781</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -619,10 +615,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>20.5</v>
+        <v>20.534500122070313</v>
       </c>
       <c r="C9">
-        <v>35.1</v>
+        <v>35.145671844482422</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -630,10 +626,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>2.1</v>
+        <v>2.0999999046325684</v>
       </c>
       <c r="C10">
-        <v>11.1</v>
+        <v>11.100000381469727</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -641,10 +637,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>2.2000000000000002</v>
+        <v>2.2343125343322754</v>
       </c>
       <c r="C11">
-        <v>16.2</v>
+        <v>16.190034866333008</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -652,10 +648,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>250.7</v>
+        <v>250.74359130859375</v>
       </c>
       <c r="C12">
-        <v>526.29999999999995</v>
+        <v>526.28076171875</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -663,10 +659,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>3.04</v>
+        <v>3.0366430282592773</v>
       </c>
       <c r="C13">
-        <v>4.45</v>
+        <v>4.4546761512756348</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -674,10 +670,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>7.5</v>
+        <v>7.4762721061706543</v>
       </c>
       <c r="C14">
-        <v>34.299999999999997</v>
+        <v>34.299999237060547</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -688,7 +684,7 @@
         <v>83</v>
       </c>
       <c r="C15">
-        <v>76.099999999999994</v>
+        <v>76.107505798339844</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -699,7 +695,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>80.099999999999994</v>
+        <v>80.147499084472656</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -710,7 +706,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>33.9</v>
+        <v>33.900001525878906</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -718,10 +714,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>57</v>
+        <v>56.959999084472656</v>
       </c>
       <c r="C18">
-        <v>17.2</v>
+        <v>17.200000762939453</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -729,10 +725,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>91.4</v>
+        <v>91.423576354980469</v>
       </c>
       <c r="C19">
-        <v>76.3</v>
+        <v>76.264350891113281</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -743,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>48.8</v>
+        <v>48.803646087646484</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,7 +761,7 @@
         <v>50</v>
       </c>
       <c r="C22">
-        <v>34.299999999999997</v>
+        <v>34.400001525878899</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -787,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>79.099999999999994</v>
+        <v>79.136253356933594</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -795,7 +791,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>40.700000000000003</v>
+        <v>40.749935150146484</v>
       </c>
       <c r="C25">
         <v>185</v>
@@ -806,10 +802,10 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>-21.1</v>
+        <v>-21.110000610351563</v>
       </c>
       <c r="C26">
-        <v>292.60000000000002</v>
+        <v>292.61001586914063</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -831,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>1.1000000000000001</v>
+        <v>1.0937001705169678</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -850,10 +846,10 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>5.8</v>
+        <v>5.7772884368896484</v>
       </c>
       <c r="C30">
-        <v>-0.3</v>
+        <v>-0.25981715321540833</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -861,10 +857,10 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>6.6</v>
+        <v>6.5520000457763672</v>
       </c>
       <c r="C31">
-        <v>20.2</v>
+        <v>20.188846588134766</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -872,10 +868,10 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>2.7</v>
+        <v>2.6800000667572021</v>
       </c>
       <c r="C32">
-        <v>7.3</v>
+        <v>7.3000001907348633</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -883,10 +879,10 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>17.3</v>
+        <v>17.258369445800781</v>
       </c>
       <c r="C33">
-        <v>7.7</v>
+        <v>7.6928410530090332</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -916,10 +912,10 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.41</v>
+        <v>0.41187998652458191</v>
       </c>
       <c r="C36">
-        <v>0.51</v>
+        <v>0.51059997081756592</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -927,10 +923,10 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>46.6</v>
+        <v>46.566299438476563</v>
       </c>
       <c r="C37">
-        <v>36.1</v>
+        <v>36.117992401123047</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -941,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="C38">
-        <v>0.64</v>
+        <v>0.63738000392913818</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -949,10 +945,10 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>35.5</v>
+        <v>35.542148590087891</v>
       </c>
       <c r="C39">
-        <v>69.2</v>
+        <v>69.19158935546875</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -985,7 +981,7 @@
         <v>50</v>
       </c>
       <c r="C42">
-        <v>10.1</v>
+        <v>10.139948844909668</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -996,7 +992,7 @@
         <v>100</v>
       </c>
       <c r="C43">
-        <v>18.3</v>
+        <v>18.323795318603516</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1018,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>58.4</v>
+        <v>58.400001525878906</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1026,10 +1022,10 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>4.2999999999999997E-2</v>
+        <v>4.3000001460313797E-2</v>
       </c>
       <c r="C46">
-        <v>0.105</v>
+        <v>0.10499999672174454</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1037,7 +1033,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>53294</v>
+        <v>53294.3046875</v>
       </c>
       <c r="C47">
         <v>23425092</v>
@@ -1048,10 +1044,10 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>-18.7</v>
+        <v>-18.700408935546875</v>
       </c>
       <c r="C48">
-        <v>9.9</v>
+        <v>9.9357528686523438</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1059,7 +1055,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>1.7</v>
+        <v>1.7000000476837158</v>
       </c>
       <c r="C49">
         <v>20</v>
@@ -1070,10 +1066,10 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>79.400000000000006</v>
+        <v>79.418800354003906</v>
       </c>
       <c r="C50">
-        <v>62.4</v>
+        <v>62.423999786376953</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1092,10 +1088,10 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>25.5</v>
+        <v>25.503353118896499</v>
       </c>
       <c r="C52">
-        <v>2.7</v>
+        <v>2.687239408493042</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1103,10 +1099,10 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>-20.9</v>
+        <v>-20.88800048828125</v>
       </c>
       <c r="C53">
-        <v>1394.3</v>
+        <v>1394.3380126953125</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1128,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>432.1</v>
+        <v>432.06146240234375</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -1136,10 +1132,10 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>1.1000000000000001</v>
+        <v>1.0884706974029541</v>
       </c>
       <c r="C56">
-        <v>14.8</v>
+        <v>14.76641845703125</v>
       </c>
     </row>
   </sheetData>
